--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-11.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_7E5D718D544A337573183F11595ED87656CDF81E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74D4947F-A610-4A19-BC17-EBAAC79EF9B9}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_7E5D718D544A337573183F11595ED87656CDF81E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A60E1A63-AEA9-4CCE-88FC-5D94C1B53258}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="110">
   <si>
     <t>Data</t>
   </si>
@@ -103,9 +103,6 @@
     <t>LAY</t>
   </si>
   <si>
-    <t>vs</t>
-  </si>
-  <si>
     <t>PENDENTE</t>
   </si>
   <si>
@@ -326,6 +323,33 @@
   </si>
   <si>
     <t>0x3</t>
+  </si>
+  <si>
+    <t>2x0</t>
+  </si>
+  <si>
+    <t>3x0</t>
+  </si>
+  <si>
+    <t>1x1</t>
+  </si>
+  <si>
+    <t>1x2</t>
+  </si>
+  <si>
+    <t>1x3</t>
+  </si>
+  <si>
+    <t>2x3</t>
+  </si>
+  <si>
+    <t>3x1</t>
+  </si>
+  <si>
+    <t>1x4</t>
+  </si>
+  <si>
+    <t>0x2</t>
   </si>
 </sst>
 </file>
@@ -788,13 +812,13 @@
         <v>100</v>
       </c>
       <c r="N2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" t="s">
         <v>28</v>
-      </c>
-      <c r="R2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -802,25 +826,25 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>31</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>32</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>33</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>35</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
       </c>
       <c r="I3" t="s">
         <v>26</v>
@@ -838,13 +862,13 @@
         <v>100</v>
       </c>
       <c r="N3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O3" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" t="s">
         <v>28</v>
-      </c>
-      <c r="R3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -852,25 +876,25 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
         <v>37</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>38</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>39</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>40</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>41</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>42</v>
-      </c>
-      <c r="H4" t="s">
-        <v>43</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -888,13 +912,13 @@
         <v>100</v>
       </c>
       <c r="N4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O4" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" t="s">
         <v>28</v>
-      </c>
-      <c r="R4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -902,25 +926,25 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
         <v>44</v>
       </c>
-      <c r="C5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>46</v>
       </c>
-      <c r="F5" t="s">
-        <v>47</v>
-      </c>
       <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
         <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
@@ -938,13 +962,13 @@
         <v>100</v>
       </c>
       <c r="N5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O5" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" t="s">
         <v>28</v>
-      </c>
-      <c r="R5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -952,25 +976,25 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
         <v>48</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>49</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>50</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>51</v>
       </c>
-      <c r="F6" t="s">
-        <v>52</v>
-      </c>
       <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
         <v>42</v>
-      </c>
-      <c r="H6" t="s">
-        <v>43</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
@@ -988,13 +1012,13 @@
         <v>100</v>
       </c>
       <c r="N6" t="s">
+        <v>101</v>
+      </c>
+      <c r="O6" t="s">
         <v>27</v>
       </c>
-      <c r="O6" t="s">
+      <c r="R6" t="s">
         <v>28</v>
-      </c>
-      <c r="R6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -1002,25 +1026,25 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s">
         <v>53</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>54</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>55</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>56</v>
       </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
       <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" t="s">
         <v>42</v>
-      </c>
-      <c r="H7" t="s">
-        <v>43</v>
       </c>
       <c r="I7" t="s">
         <v>26</v>
@@ -1038,13 +1062,13 @@
         <v>100</v>
       </c>
       <c r="N7" t="s">
+        <v>101</v>
+      </c>
+      <c r="O7" t="s">
         <v>27</v>
       </c>
-      <c r="O7" t="s">
+      <c r="R7" t="s">
         <v>28</v>
-      </c>
-      <c r="R7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -1052,25 +1076,25 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" t="s">
         <v>58</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>59</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>60</v>
       </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
       <c r="G8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" t="s">
         <v>42</v>
-      </c>
-      <c r="H8" t="s">
-        <v>43</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
@@ -1088,13 +1112,13 @@
         <v>100</v>
       </c>
       <c r="N8" t="s">
+        <v>102</v>
+      </c>
+      <c r="O8" t="s">
         <v>27</v>
       </c>
-      <c r="O8" t="s">
+      <c r="R8" t="s">
         <v>28</v>
-      </c>
-      <c r="R8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -1102,19 +1126,19 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" t="s">
         <v>62</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>63</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>64</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>65</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -1138,13 +1162,13 @@
         <v>100</v>
       </c>
       <c r="N9" t="s">
+        <v>103</v>
+      </c>
+      <c r="O9" t="s">
         <v>27</v>
       </c>
-      <c r="O9" t="s">
+      <c r="R9" t="s">
         <v>28</v>
-      </c>
-      <c r="R9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -1152,25 +1176,25 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
         <v>62</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>63</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>64</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>65</v>
       </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
       <c r="G10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" t="s">
         <v>35</v>
-      </c>
-      <c r="H10" t="s">
-        <v>36</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
@@ -1188,13 +1212,13 @@
         <v>100</v>
       </c>
       <c r="N10" t="s">
+        <v>103</v>
+      </c>
+      <c r="O10" t="s">
         <v>27</v>
       </c>
-      <c r="O10" t="s">
+      <c r="R10" t="s">
         <v>28</v>
-      </c>
-      <c r="R10" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -1202,25 +1226,25 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
         <v>67</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>68</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>69</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>70</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>71</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>72</v>
-      </c>
-      <c r="H11" t="s">
-        <v>73</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
@@ -1238,13 +1262,13 @@
         <v>100</v>
       </c>
       <c r="N11" t="s">
+        <v>104</v>
+      </c>
+      <c r="O11" t="s">
         <v>27</v>
       </c>
-      <c r="O11" t="s">
+      <c r="R11" t="s">
         <v>28</v>
-      </c>
-      <c r="R11" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -1252,19 +1276,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>68</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>69</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>70</v>
-      </c>
-      <c r="F12" t="s">
-        <v>71</v>
       </c>
       <c r="G12" t="s">
         <v>24</v>
@@ -1288,13 +1312,13 @@
         <v>100</v>
       </c>
       <c r="N12" t="s">
+        <v>104</v>
+      </c>
+      <c r="O12" t="s">
         <v>27</v>
       </c>
-      <c r="O12" t="s">
+      <c r="R12" t="s">
         <v>28</v>
-      </c>
-      <c r="R12" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -1302,25 +1326,25 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
         <v>74</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>75</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>76</v>
       </c>
-      <c r="F13" t="s">
-        <v>77</v>
-      </c>
       <c r="G13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" t="s">
         <v>42</v>
-      </c>
-      <c r="H13" t="s">
-        <v>43</v>
       </c>
       <c r="I13" t="s">
         <v>26</v>
@@ -1338,13 +1362,13 @@
         <v>100</v>
       </c>
       <c r="N13" t="s">
+        <v>98</v>
+      </c>
+      <c r="O13" t="s">
         <v>27</v>
       </c>
-      <c r="O13" t="s">
+      <c r="R13" t="s">
         <v>28</v>
-      </c>
-      <c r="R13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -1352,25 +1376,25 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" t="s">
         <v>78</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>79</v>
       </c>
-      <c r="F14" t="s">
-        <v>80</v>
-      </c>
       <c r="G14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" t="s">
         <v>42</v>
-      </c>
-      <c r="H14" t="s">
-        <v>43</v>
       </c>
       <c r="I14" t="s">
         <v>26</v>
@@ -1388,13 +1412,13 @@
         <v>100</v>
       </c>
       <c r="N14" t="s">
+        <v>106</v>
+      </c>
+      <c r="O14" t="s">
         <v>27</v>
       </c>
-      <c r="O14" t="s">
+      <c r="R14" t="s">
         <v>28</v>
-      </c>
-      <c r="R14" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -1402,25 +1426,25 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
         <v>81</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>82</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>83</v>
       </c>
-      <c r="F15" t="s">
-        <v>84</v>
-      </c>
       <c r="G15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" t="s">
         <v>35</v>
-      </c>
-      <c r="H15" t="s">
-        <v>36</v>
       </c>
       <c r="I15" t="s">
         <v>26</v>
@@ -1438,13 +1462,13 @@
         <v>100</v>
       </c>
       <c r="N15" t="s">
+        <v>105</v>
+      </c>
+      <c r="O15" t="s">
         <v>27</v>
       </c>
-      <c r="O15" t="s">
+      <c r="R15" t="s">
         <v>28</v>
-      </c>
-      <c r="R15" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -1452,25 +1476,25 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" t="s">
         <v>85</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>86</v>
       </c>
-      <c r="F16" t="s">
-        <v>87</v>
-      </c>
       <c r="G16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" t="s">
         <v>42</v>
-      </c>
-      <c r="H16" t="s">
-        <v>43</v>
       </c>
       <c r="I16" t="s">
         <v>26</v>
@@ -1488,13 +1512,13 @@
         <v>100</v>
       </c>
       <c r="N16" t="s">
+        <v>107</v>
+      </c>
+      <c r="O16" t="s">
         <v>27</v>
       </c>
-      <c r="O16" t="s">
+      <c r="R16" t="s">
         <v>28</v>
-      </c>
-      <c r="R16" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -1502,25 +1526,25 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
         <v>88</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>89</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>90</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>91</v>
       </c>
-      <c r="F17" t="s">
-        <v>92</v>
-      </c>
       <c r="G17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" t="s">
         <v>35</v>
-      </c>
-      <c r="H17" t="s">
-        <v>36</v>
       </c>
       <c r="I17" t="s">
         <v>26</v>
@@ -1538,13 +1562,13 @@
         <v>100</v>
       </c>
       <c r="N17" t="s">
+        <v>108</v>
+      </c>
+      <c r="O17" t="s">
         <v>27</v>
       </c>
-      <c r="O17" t="s">
+      <c r="R17" t="s">
         <v>28</v>
-      </c>
-      <c r="R17" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -1552,25 +1576,25 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" t="s">
         <v>93</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>94</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>95</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>96</v>
       </c>
-      <c r="F18" t="s">
-        <v>97</v>
-      </c>
       <c r="G18" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" t="s">
         <v>72</v>
-      </c>
-      <c r="H18" t="s">
-        <v>73</v>
       </c>
       <c r="I18" t="s">
         <v>26</v>
@@ -1588,13 +1612,13 @@
         <v>100</v>
       </c>
       <c r="N18" t="s">
+        <v>109</v>
+      </c>
+      <c r="O18" t="s">
         <v>27</v>
       </c>
-      <c r="O18" t="s">
+      <c r="R18" t="s">
         <v>28</v>
-      </c>
-      <c r="R18" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-11.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-11.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +623,8 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,6 +704,8 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -771,6 +785,8 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -850,6 +866,8 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -859,37 +877,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SERBIA 1</t>
+          <t>SERBIA 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Zeleznicar Pancevo x Macva Sabac</t>
+          <t>Metalac Gornji Milanovac x FK Dubocica</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zeleznicar Pancevo</t>
+          <t>Metalac Gornji Milanovac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Macva Sabac</t>
+          <t>FK Dubocica</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -898,20 +916,20 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5.9</v>
+        <v>32</v>
       </c>
       <c r="K6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>20.41</v>
+        <v>6.45</v>
       </c>
       <c r="M6" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -926,9 +944,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>6.22</v>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -938,27 +964,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DENMARK 1</t>
+          <t>SERBIA 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Copenhagen x AC Horsens</t>
+          <t>Zeleznicar Pancevo x Macva Sabac</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>Zeleznicar Pancevo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>Macva Sabac</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -977,13 +1003,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="K7" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="L7" t="n">
-        <v>19.23</v>
+        <v>20.41</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
@@ -1008,6 +1034,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1017,37 +1045,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>SERBIA 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Besiktas x Erzurum BB</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Erzurum BB</t>
-        </is>
-      </c>
+          <t>Zeleznicar Pancevo x Macva</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1056,37 +1076,45 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="L8" t="n">
-        <v>15.62</v>
+        <v>8.33</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1096,37 +1124,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AUSTRIA 1</t>
+          <t>DENMARK 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SV Ried x Red Bull Salzburg</t>
+          <t>FC Copenhagen x AC Horsens</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Red Bull Salzburg</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1135,20 +1163,20 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="L9" t="n">
-        <v>6.06</v>
+        <v>19.23</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1166,6 +1194,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1175,37 +1205,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AUSTRIA 1</t>
+          <t>TURKEY 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SV Ried x Red Bull Salzburg</t>
+          <t>Besiktas x Erzurum BB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Red Bull Salzburg</t>
+          <t>Erzurum BB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1214,20 +1244,20 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="L10" t="n">
-        <v>17.24</v>
+        <v>15.62</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1245,6 +1275,8 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1254,37 +1286,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>AUSTRIA 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nancy x Reims</t>
+          <t>SV Ried x Red Bull Salzburg</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Bull Salzburg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1293,20 +1325,20 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3.23</v>
+        <v>6.06</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1324,6 +1356,8 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1333,37 +1367,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>AUSTRIA 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nancy x Reims</t>
+          <t>SV Ried x Red Bull Salzburg</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Bull Salzburg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1372,20 +1406,20 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="L12" t="n">
-        <v>6.25</v>
+        <v>17.24</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1403,6 +1437,8 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1417,32 +1453,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NETHERLANDS 2</t>
+          <t>FRANCE 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Heracles x Jong AZ Alkmaar</t>
+          <t>Nancy x Reims</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jong AZ Alkmaar</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1451,20 +1487,20 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="K13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>15.62</v>
+        <v>3.23</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1482,6 +1518,8 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1496,32 +1534,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NETHERLANDS 2</t>
+          <t>FRANCE 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NAC Breda x Jong FC Utrecht</t>
+          <t>Nancy x Reims</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1530,20 +1568,20 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>16.67</v>
+        <v>6.25</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1561,6 +1599,8 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1575,32 +1615,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>NETHERLANDS 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Csikszereda x Dinamo Bucharest</t>
+          <t>Heracles x Jong AZ Alkmaar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Bucharest</t>
+          <t>Jong AZ Alkmaar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1609,20 +1649,20 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="K15" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="L15" t="n">
-        <v>15.15</v>
+        <v>15.62</v>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1640,6 +1680,8 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1654,22 +1696,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>NETHERLANDS 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Al Ahli x Al-Hazm (KSA)</t>
+          <t>NAC Breda x Jong FC Utrecht</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1688,20 +1730,20 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="L16" t="n">
-        <v>15.62</v>
+        <v>16.67</v>
       </c>
       <c r="M16" t="n">
         <v>100</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1719,6 +1761,8 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1728,27 +1772,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SCOTLAND 2</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Morton x Livingston</t>
+          <t>Csikszereda x Dinamo Bucharest</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Morton</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dinamo Bucharest</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1767,20 +1811,20 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="K17" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="L17" t="n">
-        <v>18.52</v>
+        <v>15.15</v>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1798,6 +1842,8 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1807,37 +1853,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PARAGUAY 1</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Club 2 de Mayo de Pedro Juan Cab x Libertad</t>
+          <t>Al Ahli x Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club 2 de Mayo de Pedro Juan Cab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1846,20 +1892,20 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="L18" t="n">
-        <v>3.03</v>
+        <v>15.62</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1877,6 +1923,8 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1886,29 +1934,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SERBIA 1</t>
+          <t>SCOTLAND 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Zeleznicar Pancevo x Macva</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+          <t>Morton x Livingston</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Livingston</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1917,43 +1973,294 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="K19" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="L19" t="n">
-        <v>8.33</v>
+        <v>18.52</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ITALY 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Pisa x Entella</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Entella</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="M20" t="n">
+        <v>200</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SPAIN 1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sevilla x Valencia</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>24</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M21" t="n">
+        <v>200</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PARAGUAY 1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Club 2 de Mayo de Pedro Juan Cab x Libertad</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Club 2 de Mayo de Pedro Juan Cab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Correct Score (0x3)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>34</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M22" t="n">
+        <v>100</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0x2</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-11.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-11.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3x3</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2241,12 +2241,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-11.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-11.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>3x3</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2241,12 +2241,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-11.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-11.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -929,19 +929,19 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -2067,19 +2067,19 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -2154,19 +2154,19 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S21" t="n">
